--- a/Result/profitability/6285.xlsx
+++ b/Result/profitability/6285.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.2</v>
       </c>
       <c r="M2" t="n">
-        <v>1.65</v>
+        <v>1.9375</v>
       </c>
       <c r="N2" t="n">
-        <v>13.10125</v>
+        <v>13.305</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.7</v>
       </c>
       <c r="M3" t="n">
-        <v>1.60125</v>
+        <v>1.7575</v>
       </c>
       <c r="N3" t="n">
-        <v>13.8375</v>
+        <v>13.855</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.87</v>
       </c>
       <c r="M4" t="n">
-        <v>1.4425</v>
+        <v>1.62625</v>
       </c>
       <c r="N4" t="n">
-        <v>14.35875</v>
+        <v>14.45875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.62</v>
       </c>
       <c r="M5" t="n">
-        <v>1.28</v>
+        <v>1.575</v>
       </c>
       <c r="N5" t="n">
-        <v>14.80375</v>
+        <v>14.985</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.86</v>
       </c>
       <c r="M6" t="n">
-        <v>1.25875</v>
+        <v>1.50875</v>
       </c>
       <c r="N6" t="n">
-        <v>15.50375</v>
+        <v>15.61375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.41</v>
       </c>
       <c r="M7" t="n">
-        <v>1.13625</v>
+        <v>1.30125</v>
       </c>
       <c r="N7" t="n">
-        <v>16.29625</v>
+        <v>16.16</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.8</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9775</v>
+        <v>1.10625</v>
       </c>
       <c r="N8" t="n">
-        <v>17.0625</v>
+        <v>16.9675</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>1.16</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8462499999999999</v>
+        <v>0.8462500000000001</v>
       </c>
       <c r="N10" t="n">
         <v>18.28</v>
@@ -1772,7 +1772,7 @@
         <v>1.39</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9325000000000001</v>
+        <v>0.9325</v>
       </c>
       <c r="N11" t="n">
         <v>18.275</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6285</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>39438</v>
+      </c>
+      <c r="D75" t="n">
+        <v>34311</v>
+      </c>
+      <c r="E75" t="n">
+        <v>5127</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2069</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.25%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-43</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2027</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1630</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.92375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>12.61875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.4364406779661019</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.7599999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.05523255813953487</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>2.29126213592233</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.449999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1255411255411254</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
